--- a/public/documents/pieces-defense/Methode-4-conso-personnel-detail.xlsx
+++ b/public/documents/pieces-defense/Methode-4-conso-personnel-detail.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>44 L = disparu Picon entier</t>
+          <t>~1,7 Picon Biere/j x 4 cl de Picon x 662 j (≈44 L)</t>
         </is>
       </c>
     </row>
